--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20211.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
   </si>
 </sst>
 </file>
@@ -495,19 +486,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,19 +512,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,19 +538,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>80.95</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -573,19 +564,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -599,19 +590,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -664,16 +655,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -687,16 +681,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -710,16 +707,19 @@
         <v>21</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>21</v>
       </c>
-      <c r="E4">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -733,16 +733,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H5">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -756,16 +759,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.84</v>
+      </c>
+      <c r="H6">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -818,19 +824,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,19 +850,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,16 +876,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>80.95</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -896,19 +902,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,19 +928,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -974,29 +980,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>17330051920191</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20211.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
   </si>
 </sst>
 </file>
@@ -486,19 +495,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -512,19 +521,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -564,19 +573,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -590,19 +599,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -655,19 +664,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -681,19 +690,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,19 +742,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -759,19 +768,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -824,19 +833,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -850,19 +859,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -888,7 +897,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -902,10 +911,10 @@
         <v>22</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>2</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -914,7 +923,7 @@
         <v>90.91</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -928,19 +937,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -980,6 +989,29 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920396</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
